--- a/data/entry_signals_us.xlsx
+++ b/data/entry_signals_us.xlsx
@@ -3387,26 +3387,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>435.88025</v>
+        <v>274.4916</v>
       </c>
       <c r="C61" t="n">
-        <v>400</v>
+        <v>260</v>
       </c>
       <c r="D61" t="n">
-        <v>1032.28</v>
+        <v>540.88</v>
       </c>
       <c r="E61" t="n">
-        <v>435.88025</v>
+        <v>274.4916</v>
       </c>
       <c r="F61" t="n">
-        <v>103.38</v>
+        <v>133.5</v>
       </c>
       <c r="G61" t="n">
-        <v>400</v>
+        <v>260</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -3424,26 +3424,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>274.4916</v>
+        <v>435.88025</v>
       </c>
       <c r="C62" t="n">
-        <v>260</v>
+        <v>400</v>
       </c>
       <c r="D62" t="n">
-        <v>540.88</v>
+        <v>1032.28</v>
       </c>
       <c r="E62" t="n">
-        <v>274.4916</v>
+        <v>435.88025</v>
       </c>
       <c r="F62" t="n">
-        <v>133.5</v>
+        <v>103.38</v>
       </c>
       <c r="G62" t="n">
-        <v>260</v>
+        <v>400</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3796,7 +3796,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
+          <t>🚨 已破止損(SL 失守, 重新評估支撐)</t>
         </is>
       </c>
       <c r="O71" t="inlineStr"/>
@@ -3991,7 +3991,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
+          <t>🚨 已破止損(SL 失守, 重新評估支撐)</t>
         </is>
       </c>
       <c r="O76" t="inlineStr"/>
@@ -4036,26 +4036,26 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>117.0715</v>
+        <v>99.6161</v>
       </c>
       <c r="C78" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D78" t="n">
-        <v>143.44</v>
+        <v>108.16</v>
       </c>
       <c r="E78" t="n">
-        <v>117.0715</v>
+        <v>99.6161</v>
       </c>
       <c r="F78" t="n">
-        <v>74.51000000000001</v>
+        <v>75.42</v>
       </c>
       <c r="G78" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4073,26 +4073,26 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NBIX</t>
+          <t>QLYS</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>142.12045</v>
+        <v>117.0715</v>
       </c>
       <c r="C79" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="D79" t="n">
-        <v>167.77</v>
+        <v>143.44</v>
       </c>
       <c r="E79" t="n">
-        <v>142.12045</v>
+        <v>117.0715</v>
       </c>
       <c r="F79" t="n">
-        <v>122.14</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4110,26 +4110,26 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>NBIX</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>99.6161</v>
+        <v>142.12045</v>
       </c>
       <c r="C80" t="n">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="D80" t="n">
-        <v>108.16</v>
+        <v>167.77</v>
       </c>
       <c r="E80" t="n">
-        <v>99.6161</v>
+        <v>142.12045</v>
       </c>
       <c r="F80" t="n">
-        <v>75.42</v>
+        <v>122.14</v>
       </c>
       <c r="G80" t="n">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -4332,26 +4332,26 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>RELX</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>28.9485</v>
+        <v>47.8882</v>
       </c>
       <c r="C86" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D86" t="n">
-        <v>31.38</v>
+        <v>48.77</v>
       </c>
       <c r="E86" t="n">
-        <v>37.93435</v>
+        <v>47.8882</v>
       </c>
       <c r="F86" t="n">
-        <v>27.57</v>
+        <v>35.12</v>
       </c>
       <c r="G86" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
@@ -4369,26 +4369,26 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>RELX</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>47.8882</v>
+        <v>28.9485</v>
       </c>
       <c r="C87" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="D87" t="n">
-        <v>48.77</v>
+        <v>31.38</v>
       </c>
       <c r="E87" t="n">
-        <v>47.8882</v>
+        <v>37.93435</v>
       </c>
       <c r="F87" t="n">
-        <v>35.12</v>
+        <v>27.57</v>
       </c>
       <c r="G87" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
@@ -4406,110 +4406,110 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>NFG</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>78.9285</v>
+        <v>63.9975</v>
       </c>
       <c r="C88" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="D88" t="n">
-        <v>77.5</v>
+        <v>63.8</v>
       </c>
       <c r="E88" t="n">
-        <v>84.4756</v>
+        <v>165.4674</v>
       </c>
       <c r="F88" t="n">
-        <v>75.17</v>
+        <v>60.95</v>
       </c>
       <c r="G88" t="n">
-        <v>101</v>
-      </c>
-      <c r="H88" t="n">
-        <v>101</v>
-      </c>
-      <c r="I88" t="n">
-        <v>78.93000000000001</v>
-      </c>
-      <c r="J88" t="n">
-        <v>84.45</v>
-      </c>
-      <c r="K88" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="L88" t="n">
-        <v>1.8</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>TP 必須 &gt; SL</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>NFG</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>50.4862</v>
+        <v>78.9285</v>
       </c>
       <c r="C89" t="n">
-        <v>35.25</v>
+        <v>101</v>
       </c>
       <c r="D89" t="n">
-        <v>51.3</v>
+        <v>77.5</v>
       </c>
       <c r="E89" t="n">
-        <v>50.4862</v>
+        <v>84.4756</v>
       </c>
       <c r="F89" t="n">
-        <v>35.45</v>
+        <v>75.17</v>
       </c>
       <c r="G89" t="n">
-        <v>35.25</v>
-      </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
+        <v>101</v>
+      </c>
+      <c r="H89" t="n">
+        <v>101</v>
+      </c>
+      <c r="I89" t="n">
+        <v>78.93000000000001</v>
+      </c>
+      <c r="J89" t="n">
+        <v>84.45</v>
+      </c>
+      <c r="K89" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1.8</v>
+      </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>TP 必須 &gt; SL</t>
-        </is>
-      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>🚨 已破止損(SL 失守, 重新評估支撐)</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>40.383</v>
+        <v>50.4862</v>
       </c>
       <c r="C90" t="n">
-        <v>34</v>
+        <v>35.25</v>
       </c>
       <c r="D90" t="n">
-        <v>44.06</v>
+        <v>51.3</v>
       </c>
       <c r="E90" t="n">
-        <v>53.99648</v>
+        <v>50.4862</v>
       </c>
       <c r="F90" t="n">
-        <v>38.46</v>
+        <v>35.45</v>
       </c>
       <c r="G90" t="n">
-        <v>34</v>
+        <v>35.25</v>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -4527,26 +4527,26 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>63.9975</v>
+        <v>40.383</v>
       </c>
       <c r="C91" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="D91" t="n">
-        <v>63.8</v>
+        <v>44.06</v>
       </c>
       <c r="E91" t="n">
-        <v>165.4674</v>
+        <v>53.99648</v>
       </c>
       <c r="F91" t="n">
-        <v>60.95</v>
+        <v>38.46</v>
       </c>
       <c r="G91" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
@@ -4603,7 +4603,7 @@
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
+          <t>🚨 已破止損(SL 失守, 重新評估支撐)</t>
         </is>
       </c>
       <c r="O92" t="inlineStr"/>
